--- a/test/standard_mapping/input_dpr.xlsx
+++ b/test/standard_mapping/input_dpr.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Program\VScode\workspace\data-governance\test\quality_check\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Program\VScode\workspace\data-governance\test\standard_mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103C566E-034E-4043-B280-A99CBDB1CB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003ABF2F-220C-4AB3-B8D2-D7C4E1D16153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2786" uniqueCount="1153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2786" uniqueCount="1154">
   <si>
     <t>上游信息</t>
   </si>
@@ -3486,6 +3486,10 @@
   </si>
   <si>
     <t>新Collection ID，催收场景的行动号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>代码枚举类</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3691,10 +3695,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4029,36 +4033,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="28" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
       <c r="Q1" s="29"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="27"/>
-      <c r="Z1" s="27"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
     </row>
     <row r="2" spans="1:26">
       <c r="A2" t="s">
@@ -4871,7 +4875,7 @@
         <v>123</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>42</v>
+        <v>1153</v>
       </c>
       <c r="V33" s="1" t="s">
         <v>43</v>

--- a/test/standard_mapping/input_dpr.xlsx
+++ b/test/standard_mapping/input_dpr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Program\VScode\workspace\data-governance\test\standard_mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003ABF2F-220C-4AB3-B8D2-D7C4E1D16153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2655BC53-A6B9-4FB8-B867-C4324E1C8419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3541,7 +3541,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3551,6 +3551,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3619,7 +3625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3686,9 +3692,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3701,6 +3704,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4033,36 +4046,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="27" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27"/>
     </row>
     <row r="2" spans="1:26">
       <c r="A2" t="s">
@@ -5201,243 +5214,243 @@
         <v>171</v>
       </c>
     </row>
-    <row r="47" spans="10:25" s="18" customFormat="1" ht="30" customHeight="1">
-      <c r="J47" s="24" t="s">
+    <row r="47" spans="10:25" s="30" customFormat="1" ht="30" customHeight="1">
+      <c r="J47" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="O47" s="24" t="s">
+      <c r="O47" s="29" t="s">
         <v>172</v>
       </c>
-      <c r="P47" s="24" t="s">
+      <c r="P47" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="Q47" s="24" t="s">
+      <c r="Q47" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="R47" s="24" t="s">
+      <c r="R47" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="V47" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="W47" s="24"/>
-      <c r="Y47" s="24" t="s">
+      <c r="V47" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="W47" s="29"/>
+      <c r="Y47" s="29" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="48" spans="10:25" s="18" customFormat="1" ht="30" customHeight="1">
-      <c r="J48" s="24" t="s">
+    <row r="48" spans="10:25" s="30" customFormat="1" ht="30" customHeight="1">
+      <c r="J48" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="O48" s="24" t="s">
+      <c r="O48" s="29" t="s">
         <v>174</v>
       </c>
-      <c r="P48" s="24" t="s">
+      <c r="P48" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="Q48" s="24" t="s">
+      <c r="Q48" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="R48" s="24" t="s">
+      <c r="R48" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="V48" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="W48" s="24"/>
-      <c r="Y48" s="24" t="s">
+      <c r="V48" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="W48" s="29"/>
+      <c r="Y48" s="29" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="49" spans="10:25" s="18" customFormat="1" ht="30" customHeight="1">
-      <c r="J49" s="24" t="s">
+    <row r="49" spans="10:25" s="30" customFormat="1" ht="30" customHeight="1">
+      <c r="J49" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="O49" s="24" t="s">
+      <c r="O49" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="P49" s="24" t="s">
+      <c r="P49" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="Q49" s="24" t="s">
+      <c r="Q49" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="R49" s="24" t="s">
+      <c r="R49" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="V49" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="W49" s="24"/>
-      <c r="Y49" s="24" t="s">
+      <c r="V49" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="W49" s="29"/>
+      <c r="Y49" s="29" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="50" spans="10:25" s="18" customFormat="1" ht="30" customHeight="1">
-      <c r="J50" s="24" t="s">
+    <row r="50" spans="10:25" s="30" customFormat="1" ht="30" customHeight="1">
+      <c r="J50" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="O50" s="24" t="s">
+      <c r="O50" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="P50" s="24" t="s">
+      <c r="P50" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="Q50" s="24" t="s">
+      <c r="Q50" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="R50" s="24" t="s">
+      <c r="R50" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="V50" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="W50" s="24"/>
-      <c r="Y50" s="24" t="s">
+      <c r="V50" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="W50" s="29"/>
+      <c r="Y50" s="29" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="51" spans="10:25" s="18" customFormat="1" ht="30" customHeight="1">
-      <c r="J51" s="24" t="s">
+    <row r="51" spans="10:25" s="30" customFormat="1" ht="30" customHeight="1">
+      <c r="J51" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="O51" s="24" t="s">
+      <c r="O51" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="P51" s="24" t="s">
+      <c r="P51" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="Q51" s="24" t="s">
+      <c r="Q51" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="R51" s="24" t="s">
+      <c r="R51" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="V51" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="W51" s="24"/>
-      <c r="Y51" s="24" t="s">
+      <c r="V51" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="W51" s="29"/>
+      <c r="Y51" s="29" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="52" spans="10:25" s="18" customFormat="1" ht="30" customHeight="1">
-      <c r="J52" s="24" t="s">
+    <row r="52" spans="10:25" s="30" customFormat="1" ht="30" customHeight="1">
+      <c r="J52" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="O52" s="24" t="s">
+      <c r="O52" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="P52" s="24" t="s">
+      <c r="P52" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="Q52" s="24" t="s">
+      <c r="Q52" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="R52" s="24" t="s">
+      <c r="R52" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="V52" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="W52" s="24"/>
-      <c r="Y52" s="24" t="s">
+      <c r="V52" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="W52" s="29"/>
+      <c r="Y52" s="29" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="53" spans="10:25" s="18" customFormat="1" ht="30" customHeight="1">
-      <c r="J53" s="24" t="s">
+    <row r="53" spans="10:25" s="30" customFormat="1" ht="30" customHeight="1">
+      <c r="J53" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="O53" s="24" t="s">
+      <c r="O53" s="29" t="s">
         <v>186</v>
       </c>
-      <c r="P53" s="24" t="s">
+      <c r="P53" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="Q53" s="24" t="s">
+      <c r="Q53" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="R53" s="24" t="s">
+      <c r="R53" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="V53" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="W53" s="24"/>
-      <c r="Y53" s="24" t="s">
+      <c r="V53" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="W53" s="29"/>
+      <c r="Y53" s="29" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="54" spans="10:25" s="18" customFormat="1" ht="30" customHeight="1">
-      <c r="J54" s="24" t="s">
+    <row r="54" spans="10:25" s="30" customFormat="1" ht="30" customHeight="1">
+      <c r="J54" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="O54" s="24" t="s">
+      <c r="O54" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="P54" s="24" t="s">
+      <c r="P54" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="Q54" s="24" t="s">
+      <c r="Q54" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="R54" s="24" t="s">
+      <c r="R54" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="V54" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="W54" s="24"/>
-      <c r="Y54" s="24" t="s">
+      <c r="V54" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="W54" s="29"/>
+      <c r="Y54" s="29" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="55" spans="10:25" s="18" customFormat="1" ht="30" customHeight="1">
-      <c r="J55" s="24" t="s">
+    <row r="55" spans="10:25" s="30" customFormat="1" ht="30" customHeight="1">
+      <c r="J55" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="O55" s="24" t="s">
+      <c r="O55" s="29" t="s">
         <v>190</v>
       </c>
-      <c r="P55" s="24" t="s">
+      <c r="P55" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="Q55" s="24" t="s">
+      <c r="Q55" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="R55" s="24" t="s">
+      <c r="R55" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="V55" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="W55" s="24"/>
-      <c r="Y55" s="24" t="s">
+      <c r="V55" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="W55" s="29"/>
+      <c r="Y55" s="29" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="56" spans="10:25" s="18" customFormat="1" ht="30" customHeight="1">
-      <c r="J56" s="24" t="s">
+    <row r="56" spans="10:25" s="30" customFormat="1" ht="30" customHeight="1">
+      <c r="J56" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="O56" s="24" t="s">
+      <c r="O56" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="P56" s="24" t="s">
+      <c r="P56" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="Q56" s="24" t="s">
+      <c r="Q56" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="R56" s="24" t="s">
+      <c r="R56" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="V56" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="W56" s="24"/>
-      <c r="Y56" s="24" t="s">
+      <c r="V56" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="W56" s="29"/>
+      <c r="Y56" s="29" t="s">
         <v>193</v>
       </c>
     </row>
@@ -7373,27 +7386,27 @@
         <v>397</v>
       </c>
     </row>
-    <row r="137" spans="10:26" ht="15" customHeight="1">
-      <c r="J137" s="7" t="s">
+    <row r="137" spans="10:26" s="30" customFormat="1" ht="15" customHeight="1">
+      <c r="J137" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="O137" s="8" t="s">
+      <c r="O137" s="32" t="s">
         <v>398</v>
       </c>
-      <c r="P137" s="7" t="s">
+      <c r="P137" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="Q137" s="8" t="s">
+      <c r="Q137" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="R137" s="8" t="s">
+      <c r="R137" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="V137" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="W137" s="8"/>
-      <c r="Y137" s="8" t="s">
+      <c r="V137" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="W137" s="32"/>
+      <c r="Y137" s="32" t="s">
         <v>399</v>
       </c>
     </row>
@@ -11005,26 +11018,26 @@
       </c>
     </row>
     <row r="286" spans="10:25" s="18" customFormat="1" ht="15" customHeight="1">
-      <c r="J286" s="25" t="s">
+      <c r="J286" s="24" t="s">
         <v>854</v>
       </c>
-      <c r="O286" s="25" t="s">
+      <c r="O286" s="24" t="s">
         <v>855</v>
       </c>
-      <c r="P286" s="26" t="s">
+      <c r="P286" s="25" t="s">
         <v>856</v>
       </c>
-      <c r="Q286" s="25" t="s">
+      <c r="Q286" s="24" t="s">
         <v>857</v>
       </c>
-      <c r="R286" s="25" t="s">
+      <c r="R286" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="V286" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="W286" s="25"/>
-      <c r="Y286" s="25" t="s">
+      <c r="V286" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="W286" s="24"/>
+      <c r="Y286" s="24" t="s">
         <v>855</v>
       </c>
     </row>
@@ -12347,74 +12360,74 @@
       </c>
     </row>
     <row r="341" spans="10:25" s="18" customFormat="1" ht="15" customHeight="1">
-      <c r="J341" s="25" t="s">
+      <c r="J341" s="24" t="s">
         <v>1015</v>
       </c>
-      <c r="O341" s="25" t="s">
+      <c r="O341" s="24" t="s">
         <v>1016</v>
       </c>
-      <c r="P341" s="26" t="s">
+      <c r="P341" s="25" t="s">
         <v>435</v>
       </c>
-      <c r="Q341" s="25" t="s">
+      <c r="Q341" s="24" t="s">
         <v>1017</v>
       </c>
-      <c r="R341" s="25" t="s">
+      <c r="R341" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="V341" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="W341" s="25"/>
-      <c r="Y341" s="25" t="s">
+      <c r="V341" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="W341" s="24"/>
+      <c r="Y341" s="24" t="s">
         <v>1018</v>
       </c>
     </row>
     <row r="342" spans="10:25" s="18" customFormat="1" ht="15" customHeight="1">
-      <c r="J342" s="25" t="s">
+      <c r="J342" s="24" t="s">
         <v>1015</v>
       </c>
-      <c r="O342" s="25" t="s">
+      <c r="O342" s="24" t="s">
         <v>1019</v>
       </c>
-      <c r="P342" s="26" t="s">
+      <c r="P342" s="25" t="s">
         <v>435</v>
       </c>
-      <c r="Q342" s="25" t="s">
+      <c r="Q342" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="R342" s="25" t="s">
+      <c r="R342" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="V342" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="W342" s="25"/>
-      <c r="Y342" s="25" t="s">
+      <c r="V342" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="W342" s="24"/>
+      <c r="Y342" s="24" t="s">
         <v>1020</v>
       </c>
     </row>
     <row r="343" spans="10:25" s="18" customFormat="1" ht="15" customHeight="1">
-      <c r="J343" s="25" t="s">
+      <c r="J343" s="24" t="s">
         <v>1015</v>
       </c>
-      <c r="O343" s="25" t="s">
+      <c r="O343" s="24" t="s">
         <v>1021</v>
       </c>
-      <c r="P343" s="26" t="s">
+      <c r="P343" s="25" t="s">
         <v>435</v>
       </c>
-      <c r="Q343" s="25" t="s">
+      <c r="Q343" s="24" t="s">
         <v>1022</v>
       </c>
-      <c r="R343" s="25" t="s">
+      <c r="R343" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="V343" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="W343" s="25"/>
-      <c r="Y343" s="25" t="s">
+      <c r="V343" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="W343" s="24"/>
+      <c r="Y343" s="24" t="s">
         <v>1023</v>
       </c>
     </row>
